--- a/src/test/resources/testData/Opencart_LoginData.xlsx
+++ b/src/test/resources/testData/Opencart_LoginData.xlsx
@@ -3,12 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\SeleniumFramework\SeleniumJavaFramework\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE3D1F2-DE73-4738-A5A7-5041F35950FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DEB45B29-163A-440A-B226-29DC10965F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -16,6 +11,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
   <si>
     <t>username</t>
   </si>
@@ -64,9 +60,6 @@
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>xyz123fed3</t>
@@ -127,21 +120,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
+        <fgColor indexed="11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
         <fgColor indexed="10"/>
       </patternFill>
     </fill>
@@ -174,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -194,16 +187,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -548,7 +543,7 @@
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="16">
+      <c r="D2" s="15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -560,10 +555,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s" s="17">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.5">
@@ -571,13 +566,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s" s="18">
-        <v>15</v>
+      <c r="D4" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.5">
@@ -590,7 +585,7 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" t="s" s="13">
+      <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -602,7 +597,7 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" t="s" s="14">
+      <c r="D6" s="19" t="s">
         <v>12</v>
       </c>
     </row>
@@ -614,7 +609,7 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" t="s" s="15">
+      <c r="D7" s="20" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/test/resources/testData/Opencart_LoginData.xlsx
+++ b/src/test/resources/testData/Opencart_LoginData.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="15">
   <si>
     <t>username</t>
   </si>
@@ -167,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -187,6 +187,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
@@ -543,7 +555,7 @@
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="27" t="s">
         <v>12</v>
       </c>
     </row>
@@ -557,7 +569,7 @@
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="28" t="s">
         <v>14</v>
       </c>
     </row>
@@ -571,7 +583,7 @@
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="29" t="s">
         <v>12</v>
       </c>
     </row>
@@ -585,7 +597,7 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="30" t="s">
         <v>12</v>
       </c>
     </row>
@@ -597,7 +609,7 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="31" t="s">
         <v>12</v>
       </c>
     </row>
@@ -609,7 +621,7 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="32" t="s">
         <v>12</v>
       </c>
     </row>

--- a/src/test/resources/testData/Opencart_LoginData.xlsx
+++ b/src/test/resources/testData/Opencart_LoginData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DEB45B29-163A-440A-B226-29DC10965F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{786512C6-EE25-4767-9A02-050CFAC31D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <calcPr calcId="0"/>
   <oleSize ref="A1"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>username</t>
   </si>
@@ -72,7 +72,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -105,7 +104,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,16 +120,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="11"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +156,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -187,30 +176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -529,9 +495,9 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.26953125"/>
-    <col min="2" max="2" customWidth="true" width="17.26953125"/>
-    <col min="3" max="3" customWidth="true" width="18.1796875"/>
+    <col min="1" max="1" width="37.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+    <col min="3" max="3" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
@@ -555,7 +521,7 @@
       <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -567,9 +533,9 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -583,7 +549,7 @@
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -597,7 +563,7 @@
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -609,7 +575,7 @@
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -621,7 +587,7 @@
       <c r="C7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
